--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3748"/>
+  <dimension ref="A1:E3749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101612,6 +101612,33 @@
         </is>
       </c>
     </row>
+    <row r="3749">
+      <c r="A3749" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B3749" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3749" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D3749" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E3749" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3749"/>
+  <dimension ref="A1:E3750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101639,6 +101639,33 @@
         </is>
       </c>
     </row>
+    <row r="3750">
+      <c r="A3750" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B3750" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3750" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3750" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E3750" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3750"/>
+  <dimension ref="A1:E3751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101666,6 +101666,33 @@
         </is>
       </c>
     </row>
+    <row r="3751">
+      <c r="A3751" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B3751" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3751" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3751" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3751" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3751"/>
+  <dimension ref="A1:E3752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101693,6 +101693,33 @@
         </is>
       </c>
     </row>
+    <row r="3752">
+      <c r="A3752" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B3752" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3752" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3752" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3752" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3752"/>
+  <dimension ref="A1:E3753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101720,6 +101720,33 @@
         </is>
       </c>
     </row>
+    <row r="3753">
+      <c r="A3753" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B3753" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3753" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3753" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3753" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3753"/>
+  <dimension ref="A1:E3754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101747,6 +101747,33 @@
         </is>
       </c>
     </row>
+    <row r="3754">
+      <c r="A3754" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B3754" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3754" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3754" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3754" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3754"/>
+  <dimension ref="A1:E3755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101774,6 +101774,33 @@
         </is>
       </c>
     </row>
+    <row r="3755">
+      <c r="A3755" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B3755" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3755" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3755" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E3755" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3755"/>
+  <dimension ref="A1:E3756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101801,6 +101801,33 @@
         </is>
       </c>
     </row>
+    <row r="3756">
+      <c r="A3756" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B3756" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3756" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3756" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E3756" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3756"/>
+  <dimension ref="A1:E3758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101828,6 +101828,60 @@
         </is>
       </c>
     </row>
+    <row r="3757">
+      <c r="A3757" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B3757" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3757" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3757" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E3757" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3758">
+      <c r="A3758" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B3758" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3758" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3758" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3758" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3758"/>
+  <dimension ref="A1:E3759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101882,6 +101882,33 @@
         </is>
       </c>
     </row>
+    <row r="3759">
+      <c r="A3759" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B3759" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3759" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3759" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E3759" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3759"/>
+  <dimension ref="A1:E3760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101909,6 +101909,33 @@
         </is>
       </c>
     </row>
+    <row r="3760">
+      <c r="A3760" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B3760" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3760" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3760" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E3760" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3760"/>
+  <dimension ref="A1:E3761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101936,6 +101936,33 @@
         </is>
       </c>
     </row>
+    <row r="3761">
+      <c r="A3761" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B3761" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3761" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3761" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3761" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3761"/>
+  <dimension ref="A1:E3762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101963,6 +101963,33 @@
         </is>
       </c>
     </row>
+    <row r="3762">
+      <c r="A3762" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B3762" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3762" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D3762" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3762" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3762"/>
+  <dimension ref="A1:E3763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101990,6 +101990,33 @@
         </is>
       </c>
     </row>
+    <row r="3763">
+      <c r="A3763" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B3763" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3763" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3763" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3763" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3763"/>
+  <dimension ref="A1:E3764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102017,6 +102017,33 @@
         </is>
       </c>
     </row>
+    <row r="3764">
+      <c r="A3764" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B3764" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3764" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3764" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3764" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3764"/>
+  <dimension ref="A1:E3765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102044,6 +102044,33 @@
         </is>
       </c>
     </row>
+    <row r="3765">
+      <c r="A3765" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B3765" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3765" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D3765" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3765" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3765"/>
+  <dimension ref="A1:E3766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102071,6 +102071,33 @@
         </is>
       </c>
     </row>
+    <row r="3766">
+      <c r="A3766" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B3766" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3766" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D3766" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3766" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3766"/>
+  <dimension ref="A1:E3767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102098,6 +102098,33 @@
         </is>
       </c>
     </row>
+    <row r="3767">
+      <c r="A3767" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B3767" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3767" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D3767" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E3767" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3767"/>
+  <dimension ref="A1:E3768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102125,6 +102125,33 @@
         </is>
       </c>
     </row>
+    <row r="3768">
+      <c r="A3768" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B3768" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3768" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3768" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E3768" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3768"/>
+  <dimension ref="A1:E3769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102152,6 +102152,33 @@
         </is>
       </c>
     </row>
+    <row r="3769">
+      <c r="A3769" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B3769" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3769" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D3769" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3769" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3769"/>
+  <dimension ref="A1:E3770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102179,6 +102179,33 @@
         </is>
       </c>
     </row>
+    <row r="3770">
+      <c r="A3770" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B3770" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3770" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3770" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3770" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3770"/>
+  <dimension ref="A1:E3771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102206,6 +102206,33 @@
         </is>
       </c>
     </row>
+    <row r="3771">
+      <c r="A3771" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B3771" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3771" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3771" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3771" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3771"/>
+  <dimension ref="A1:E3772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102233,6 +102233,33 @@
         </is>
       </c>
     </row>
+    <row r="3772">
+      <c r="A3772" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B3772" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3772" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D3772" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3772" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3772"/>
+  <dimension ref="A1:E3773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102260,6 +102260,33 @@
         </is>
       </c>
     </row>
+    <row r="3773">
+      <c r="A3773" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B3773" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3773" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D3773" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3773" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3773"/>
+  <dimension ref="A1:E3774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102287,6 +102287,33 @@
         </is>
       </c>
     </row>
+    <row r="3774">
+      <c r="A3774" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B3774" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3774" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3774" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3774" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3774"/>
+  <dimension ref="A1:E3775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102314,6 +102314,33 @@
         </is>
       </c>
     </row>
+    <row r="3775">
+      <c r="A3775" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B3775" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3775" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D3775" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3775" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3775"/>
+  <dimension ref="A1:E3776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102341,6 +102341,33 @@
         </is>
       </c>
     </row>
+    <row r="3776">
+      <c r="A3776" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B3776" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3776" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3776" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3776" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3776"/>
+  <dimension ref="A1:E3777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102368,6 +102368,33 @@
         </is>
       </c>
     </row>
+    <row r="3777">
+      <c r="A3777" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B3777" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3777" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3777" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3777" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3777"/>
+  <dimension ref="A1:E3778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102395,6 +102395,33 @@
         </is>
       </c>
     </row>
+    <row r="3778">
+      <c r="A3778" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B3778" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3778" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3778" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3778" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3778"/>
+  <dimension ref="A1:E3779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102422,6 +102422,33 @@
         </is>
       </c>
     </row>
+    <row r="3779">
+      <c r="A3779" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B3779" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3779" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D3779" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3779" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3779"/>
+  <dimension ref="A1:E3780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102449,6 +102449,33 @@
         </is>
       </c>
     </row>
+    <row r="3780">
+      <c r="A3780" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B3780" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3780" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3780" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3780" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3780"/>
+  <dimension ref="A1:E3781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102476,6 +102476,33 @@
         </is>
       </c>
     </row>
+    <row r="3781">
+      <c r="A3781" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B3781" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3781" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3781" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3781" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3781"/>
+  <dimension ref="A1:E3782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102503,6 +102503,33 @@
         </is>
       </c>
     </row>
+    <row r="3782">
+      <c r="A3782" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B3782" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3782" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3782" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3782" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3782"/>
+  <dimension ref="A1:E3783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102530,6 +102530,33 @@
         </is>
       </c>
     </row>
+    <row r="3783">
+      <c r="A3783" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B3783" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3783" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3783" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3783" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3783"/>
+  <dimension ref="A1:E3784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102557,6 +102557,33 @@
         </is>
       </c>
     </row>
+    <row r="3784">
+      <c r="A3784" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B3784" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3784" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D3784" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3784" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3784"/>
+  <dimension ref="A1:E3785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102584,6 +102584,33 @@
         </is>
       </c>
     </row>
+    <row r="3785">
+      <c r="A3785" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B3785" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3785" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D3785" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3785" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3785"/>
+  <dimension ref="A1:E3786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102611,6 +102611,33 @@
         </is>
       </c>
     </row>
+    <row r="3786">
+      <c r="A3786" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B3786" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3786" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D3786" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3786" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3786"/>
+  <dimension ref="A1:E3787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102638,6 +102638,33 @@
         </is>
       </c>
     </row>
+    <row r="3787">
+      <c r="A3787" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B3787" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3787" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D3787" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3787" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3787"/>
+  <dimension ref="A1:E3788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102665,6 +102665,33 @@
         </is>
       </c>
     </row>
+    <row r="3788">
+      <c r="A3788" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B3788" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3788" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3788" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E3788" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3788"/>
+  <dimension ref="A1:E3789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102692,6 +102692,33 @@
         </is>
       </c>
     </row>
+    <row r="3789">
+      <c r="A3789" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B3789" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3789" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D3789" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3789" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3789"/>
+  <dimension ref="A1:E3790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102719,6 +102719,33 @@
         </is>
       </c>
     </row>
+    <row r="3790">
+      <c r="A3790" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B3790" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3790" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3790" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E3790" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3790"/>
+  <dimension ref="A1:E3791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102746,6 +102746,33 @@
         </is>
       </c>
     </row>
+    <row r="3791">
+      <c r="A3791" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B3791" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3791" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3791" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3791" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3791"/>
+  <dimension ref="A1:E3792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102773,6 +102773,33 @@
         </is>
       </c>
     </row>
+    <row r="3792">
+      <c r="A3792" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B3792" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3792" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3792" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3792" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3792"/>
+  <dimension ref="A1:E3793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102800,6 +102800,33 @@
         </is>
       </c>
     </row>
+    <row r="3793">
+      <c r="A3793" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3793" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3793" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3793" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3793" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3793"/>
+  <dimension ref="A1:E3794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -102824,6 +102836,33 @@
       <c r="E3793" t="inlineStr">
         <is>
           <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="3794">
+      <c r="A3794" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3794" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3794" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D3794" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3794" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3794"/>
+  <dimension ref="A1:E3795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102866,6 +102866,33 @@
         </is>
       </c>
     </row>
+    <row r="3795">
+      <c r="A3795" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B3795" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3795" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D3795" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3795" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3795"/>
+  <dimension ref="A1:E3796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102893,6 +102893,33 @@
         </is>
       </c>
     </row>
+    <row r="3796">
+      <c r="A3796" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B3796" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3796" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3796" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3796" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3796"/>
+  <dimension ref="A1:E3797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -102917,6 +102905,33 @@
       <c r="E3796" t="inlineStr">
         <is>
           <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3797">
+      <c r="A3797" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B3797" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3797" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3797" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3797" t="inlineStr">
+        <is>
+          <t>63</t>
         </is>
       </c>
     </row>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3797"/>
+  <dimension ref="A1:E3798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102935,6 +102935,33 @@
         </is>
       </c>
     </row>
+    <row r="3798">
+      <c r="A3798" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B3798" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3798" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3798" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3798" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3798"/>
+  <dimension ref="A1:E3799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102962,6 +102962,33 @@
         </is>
       </c>
     </row>
+    <row r="3799">
+      <c r="A3799" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B3799" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3799" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3799" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3799" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3799"/>
+  <dimension ref="A1:E3800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102989,6 +102989,33 @@
         </is>
       </c>
     </row>
+    <row r="3800">
+      <c r="A3800" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B3800" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3800" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3800" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3800" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3800"/>
+  <dimension ref="A1:E3801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103016,6 +103016,33 @@
         </is>
       </c>
     </row>
+    <row r="3801">
+      <c r="A3801" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B3801" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3801" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D3801" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3801" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3801"/>
+  <dimension ref="A1:E3803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103043,6 +103043,60 @@
         </is>
       </c>
     </row>
+    <row r="3802">
+      <c r="A3802" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B3802" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3802" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3802" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3802" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="3803">
+      <c r="A3803" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B3803" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3803" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D3803" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3803" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3803"/>
+  <dimension ref="A1:E3805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103097,6 +103097,60 @@
         </is>
       </c>
     </row>
+    <row r="3804">
+      <c r="A3804" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B3804" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3804" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3804" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3804" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3805">
+      <c r="A3805" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B3805" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3805" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3805" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3805" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3805"/>
+  <dimension ref="A1:E3806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103151,6 +103151,33 @@
         </is>
       </c>
     </row>
+    <row r="3806">
+      <c r="A3806" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B3806" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3806" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D3806" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3806" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3806"/>
+  <dimension ref="A1:E3807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103178,6 +103178,33 @@
         </is>
       </c>
     </row>
+    <row r="3807">
+      <c r="A3807" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B3807" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3807" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D3807" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3807" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3807"/>
+  <dimension ref="A1:E3808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103205,6 +103205,33 @@
         </is>
       </c>
     </row>
+    <row r="3808">
+      <c r="A3808" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B3808" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3808" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3808" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3808" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3808"/>
+  <dimension ref="A1:E3809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103232,6 +103232,33 @@
         </is>
       </c>
     </row>
+    <row r="3809">
+      <c r="A3809" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B3809" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3809" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D3809" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3809" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3809"/>
+  <dimension ref="A1:E3810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103259,6 +103259,33 @@
         </is>
       </c>
     </row>
+    <row r="3810">
+      <c r="A3810" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B3810" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3810" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D3810" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3810" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3810"/>
+  <dimension ref="A1:E3811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103286,6 +103286,33 @@
         </is>
       </c>
     </row>
+    <row r="3811">
+      <c r="A3811" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B3811" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3811" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3811" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E3811" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3811"/>
+  <dimension ref="A1:E3812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103313,6 +103313,33 @@
         </is>
       </c>
     </row>
+    <row r="3812">
+      <c r="A3812" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B3812" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3812" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3812" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3812" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3812"/>
+  <dimension ref="A1:E3813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103340,6 +103340,33 @@
         </is>
       </c>
     </row>
+    <row r="3813">
+      <c r="A3813" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B3813" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3813" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D3813" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E3813" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3813"/>
+  <dimension ref="A1:E3815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103367,6 +103367,60 @@
         </is>
       </c>
     </row>
+    <row r="3814">
+      <c r="A3814" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B3814" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3814" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D3814" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3814" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3815">
+      <c r="A3815" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B3815" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3815" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D3815" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3815" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3815"/>
+  <dimension ref="A1:E3816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103421,6 +103421,33 @@
         </is>
       </c>
     </row>
+    <row r="3816">
+      <c r="A3816" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3816" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3816" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3816" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E3816" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3816"/>
+  <dimension ref="A1:E3817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103448,6 +103448,33 @@
         </is>
       </c>
     </row>
+    <row r="3817">
+      <c r="A3817" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3817" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3817" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3817" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3817" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3817"/>
+  <dimension ref="A1:E3818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103475,6 +103475,33 @@
         </is>
       </c>
     </row>
+    <row r="3818">
+      <c r="A3818" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B3818" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3818" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D3818" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3818" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3818"/>
+  <dimension ref="A1:E3819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103502,6 +103502,33 @@
         </is>
       </c>
     </row>
+    <row r="3819">
+      <c r="A3819" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B3819" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3819" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D3819" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E3819" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3819"/>
+  <dimension ref="A1:E3820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103529,6 +103529,33 @@
         </is>
       </c>
     </row>
+    <row r="3820">
+      <c r="A3820" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B3820" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3820" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D3820" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E3820" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3820"/>
+  <dimension ref="A1:E3821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103556,6 +103556,33 @@
         </is>
       </c>
     </row>
+    <row r="3821">
+      <c r="A3821" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B3821" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3821" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3821" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3821" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3821"/>
+  <dimension ref="A1:E3822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103583,6 +103583,33 @@
         </is>
       </c>
     </row>
+    <row r="3822">
+      <c r="A3822" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B3822" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3822" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D3822" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3822" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3822"/>
+  <dimension ref="A1:E3823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103610,6 +103610,33 @@
         </is>
       </c>
     </row>
+    <row r="3823">
+      <c r="A3823" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B3823" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3823" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3823" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E3823" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3823"/>
+  <dimension ref="A1:E3824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103637,6 +103637,33 @@
         </is>
       </c>
     </row>
+    <row r="3824">
+      <c r="A3824" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B3824" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3824" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D3824" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E3824" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3824"/>
+  <dimension ref="A1:E3825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103664,6 +103664,33 @@
         </is>
       </c>
     </row>
+    <row r="3825">
+      <c r="A3825" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B3825" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3825" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3825" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3825" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3825"/>
+  <dimension ref="A1:E3826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103691,6 +103691,33 @@
         </is>
       </c>
     </row>
+    <row r="3826">
+      <c r="A3826" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B3826" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3826" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3826" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3826" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3826"/>
+  <dimension ref="A1:E3827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103718,6 +103718,33 @@
         </is>
       </c>
     </row>
+    <row r="3827">
+      <c r="A3827" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B3827" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3827" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3827" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3827" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3827"/>
+  <dimension ref="A1:E3828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103745,6 +103745,33 @@
         </is>
       </c>
     </row>
+    <row r="3828">
+      <c r="A3828" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B3828" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3828" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3828" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3828" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
